--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260516_204017.xlsx
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
